--- a/Minor Test Tasks.xlsx
+++ b/Minor Test Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DMY\GM\Assessment\Development_Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06560C2B-3230-494A-941B-C31496FE7DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C40660A-EB23-4051-A04B-51119548C530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,10 @@
     <sheet name="Queries(done)" sheetId="1" r:id="rId1"/>
     <sheet name="XMLport(done)" sheetId="4" r:id="rId2"/>
     <sheet name="File Operations(done)" sheetId="3" r:id="rId3"/>
-    <sheet name="Design" sheetId="7" r:id="rId4"/>
-    <sheet name="Add-ins" sheetId="2" r:id="rId5"/>
-    <sheet name="References" sheetId="5" r:id="rId6"/>
-    <sheet name="Permissions" sheetId="6" r:id="rId7"/>
+    <sheet name="Design(done)" sheetId="7" r:id="rId4"/>
+    <sheet name="Add-ins(doesn't work)" sheetId="2" r:id="rId5"/>
+    <sheet name="References(done)" sheetId="5" r:id="rId6"/>
+    <sheet name="Permissions(DONE)" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="133">
   <si>
     <t>Query Customers with Sales Orders</t>
   </si>
@@ -495,6 +495,12 @@
   </si>
   <si>
     <t>DONE during ATEA Upgrade</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>doesn’t work</t>
   </si>
 </sst>
 </file>
@@ -551,7 +557,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -561,6 +567,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,7 +590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -593,6 +605,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -984,9 +997,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>130</v>
-      </c>
+      <c r="E1" s="9"/>
       <c r="F1" s="9"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -1528,60 +1539,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1C8B9F0-D057-4BEB-B7BB-BE31979B183E}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="F1" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
         <v>99</v>
       </c>
@@ -1687,73 +1701,76 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F315F232-DA43-4FAF-A01C-6813BA79D17E}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
         <v>128</v>
+      </c>
+      <c r="G16" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
